--- a/Catch and index models/Sintese_3_modelos/tabela_comparacao_modelos.xlsx
+++ b/Catch and index models/Sintese_3_modelos/tabela_comparacao_modelos.xlsx
@@ -64,7 +64,7 @@
     <t>0,40 (0,11–0,92)</t>
   </si>
   <si>
-    <t>0,70 – 2,34</t>
+    <t>0,69 – 2,34</t>
   </si>
   <si>
     <t>0,05 – 0,20</t>
